--- a/omicron/xlsx/845-VEC-test-plan.xlsx
+++ b/omicron/xlsx/845-VEC-test-plan.xlsx
@@ -646,11 +646,11 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>generated 2026-09-05 12:27 from index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
+          <t>generated 2026-09-15 00:32 from 845.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Configuration</t>
@@ -658,7 +658,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>mva=20; kv1=115; kv2=13.8; vg=Dyn1; freq=60; rot=ABC; ct1p=150; ct1s=5; ct1c=wye; ct2p=1200; ct2s=5; ct2c=wye; ctgp=200; ctgs=5; refw=2; vtp=13800; vts=120; vtc=wye; vtw=2; cmc=6x; imax=12.5; vmax=300</t>
+          <t>mva=20; mva2=26.7; mva3=33.3; mvaBase=onan; kv1=115; kv2=13.8; freq=60; rot=ABC; w1c=D; w2c=YN; clk=1; z=8.5; xr=12; oltcW=1; oltcHi=10; oltcLo=10; oltcN=16; oltcPos=0; gnd1=none; gnd1v=0; gnd2=ngrA; gnd2v=400; ct1p=150; ct1s=5; ct1c=wye; ct2p=1200; ct2s=5; ct2c=wye; ctgp=200; ctgs=5; refw=2; vtp=13800; vts=120; vtc=wye; vtw=2; cmc=6x; imax=12.5; vmax=300</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Phase L1 and ground input driven in opposition at 4.0 ×CT — an external ground fault.</t>
+          <t>Phase L1 and ground input driven in opposition at 4 ×CT — an external ground fault.</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>20.0000@180.0</t>
+          <t>120.0000@180.0</t>
         </is>
       </c>
       <c r="P16" s="12" t="n"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>1.155 pu V/Hz requires 80.02 V secondary at 60.0 Hz</t>
+          <t>1.155 pu V/Hz requires 80.02 V secondary at 60 Hz</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>1.045 pu V/Hz requires 72.40 V secondary at 60.0 Hz</t>
+          <t>1.045 pu V/Hz requires 72.40 V secondary at 60 Hz</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>1.155 pu V/Hz requires 76.02 V secondary at 57.0 Hz</t>
+          <t>1.155 pu V/Hz requires 76.02 V secondary at 57 Hz</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>1.045 pu V/Hz requires 68.78 V secondary at 57.0 Hz</t>
+          <t>1.045 pu V/Hz requires 68.78 V secondary at 57 Hz</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>1.155 pu V/Hz requires 72.02 V secondary at 54.0 Hz</t>
+          <t>1.155 pu V/Hz requires 72.02 V secondary at 54 Hz</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>1.045 pu V/Hz requires 65.16 V secondary at 54.0 Hz</t>
+          <t>1.045 pu V/Hz requires 65.16 V secondary at 54 Hz</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>Initiate asserted with current held at 2.0× detector and never removed</t>
+          <t>Initiate asserted with current held at 2× detector and never removed</t>
         </is>
       </c>
       <c r="H83" s="15" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H2" s="11" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — above slope</t>
+          <t>Irest 0.5 pu — above slope</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Irest 0.50 pu — below slope</t>
+          <t>Irest 0.5 pu — below slope</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — above slope</t>
+          <t>Irest 1.5 pu — above slope</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Irest 1.50 pu — below slope</t>
+          <t>Irest 1.5 pu — below slope</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — above slope</t>
+          <t>Irest 3 pu — above slope</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Irest 3.00 pu — below slope</t>
+          <t>Irest 3 pu — below slope</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — above slope</t>
+          <t>Irest 7 pu — above slope</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Irest 7.00 pu — below slope</t>
+          <t>Irest 7 pu — below slope</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -17546,7 +17546,7 @@
         </is>
       </c>
       <c r="I108" s="12" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="G156" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H158" s="11" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -21181,7 +21181,7 @@
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="G162" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H166" s="11" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="G168" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H168" s="11" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H170" s="11" t="inlineStr">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H174" s="11" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="G178" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H178" s="11" t="inlineStr">
@@ -22511,7 +22511,7 @@
       </c>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H180" s="11" t="inlineStr">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="G199" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="G201" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="G202" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G203" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr">
@@ -24261,7 +24261,7 @@
       </c>
       <c r="G204" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="G205" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="G206" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="G207" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H226" s="11" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H227" s="11" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G228" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H228" s="11" t="inlineStr">
@@ -26011,7 +26011,7 @@
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H229" s="11" t="inlineStr">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H230" s="11" t="inlineStr">
@@ -26151,7 +26151,7 @@
       </c>
       <c r="G231" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H231" s="11" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="G232" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H232" s="11" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H233" s="11" t="inlineStr">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="G234" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H234" s="11" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H235" s="11" t="inlineStr">
@@ -26501,7 +26501,7 @@
       </c>
       <c r="G236" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H236" s="11" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="G237" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H237" s="11" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H238" s="11" t="inlineStr">
@@ -26711,7 +26711,7 @@
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H239" s="11" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="G240" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H240" s="11" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H241" s="11" t="inlineStr">
@@ -26921,7 +26921,7 @@
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H242" s="11" t="inlineStr">
@@ -26991,7 +26991,7 @@
       </c>
       <c r="G243" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H243" s="11" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H244" s="11" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H245" s="11" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H246" s="11" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G247" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H247" s="11" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H248" s="11" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H249" s="11" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H250" s="11" t="inlineStr">
@@ -27551,7 +27551,7 @@
       </c>
       <c r="G251" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H251" s="11" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="G252" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H252" s="11" t="inlineStr">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="G271" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H271" s="14" t="inlineStr">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="G272" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H272" s="14" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="G273" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H273" s="14" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="G274" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H274" s="14" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="G275" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H275" s="14" t="inlineStr">
@@ -29301,7 +29301,7 @@
       </c>
       <c r="G276" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H276" s="14" t="inlineStr">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="G277" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H277" s="14" t="inlineStr">
@@ -29441,7 +29441,7 @@
       </c>
       <c r="G278" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H278" s="14" t="inlineStr">
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G279" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H279" s="14" t="inlineStr">
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G298" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H298" s="11" t="inlineStr">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="G299" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="G300" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H300" s="11" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="G301" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H301" s="11" t="inlineStr">
@@ -31121,7 +31121,7 @@
       </c>
       <c r="G302" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H302" s="11" t="inlineStr">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="G303" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H303" s="11" t="inlineStr">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G304" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H304" s="11" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="G305" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H305" s="11" t="inlineStr">
@@ -31401,7 +31401,7 @@
       </c>
       <c r="G306" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H306" s="11" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="G307" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H307" s="11" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="G308" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H308" s="11" t="inlineStr">
@@ -31611,7 +31611,7 @@
       </c>
       <c r="G309" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H309" s="11" t="inlineStr">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="G310" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H310" s="11" t="inlineStr">
@@ -31751,7 +31751,7 @@
       </c>
       <c r="G311" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H311" s="11" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="G312" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H312" s="11" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="G313" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H313" s="11" t="inlineStr">
@@ -31961,7 +31961,7 @@
       </c>
       <c r="G314" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H314" s="11" t="inlineStr">
@@ -32031,7 +32031,7 @@
       </c>
       <c r="G315" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H315" s="11" t="inlineStr">
@@ -32101,7 +32101,7 @@
       </c>
       <c r="G316" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H316" s="11" t="inlineStr">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G317" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H317" s="11" t="inlineStr">
@@ -32241,7 +32241,7 @@
       </c>
       <c r="G318" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H318" s="11" t="inlineStr">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="G319" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H319" s="11" t="inlineStr">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="G320" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H320" s="11" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="G321" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H321" s="11" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H322" s="11" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G323" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H323" s="11" t="inlineStr">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="G324" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H324" s="11" t="inlineStr">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="G343" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H343" s="14" t="inlineStr">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="G344" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H344" s="14" t="inlineStr">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="G345" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H345" s="14" t="inlineStr">
@@ -34201,7 +34201,7 @@
       </c>
       <c r="G346" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H346" s="14" t="inlineStr">
@@ -34271,7 +34271,7 @@
       </c>
       <c r="G347" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H347" s="14" t="inlineStr">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="G348" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H348" s="14" t="inlineStr">
@@ -34411,7 +34411,7 @@
       </c>
       <c r="G349" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H349" s="14" t="inlineStr">
@@ -34481,7 +34481,7 @@
       </c>
       <c r="G350" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H350" s="14" t="inlineStr">
@@ -34551,7 +34551,7 @@
       </c>
       <c r="G351" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H351" s="14" t="inlineStr">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="G370" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H370" s="11" t="inlineStr">
@@ -35951,7 +35951,7 @@
       </c>
       <c r="G371" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H371" s="11" t="inlineStr">
@@ -36021,7 +36021,7 @@
       </c>
       <c r="G372" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H372" s="11" t="inlineStr">
@@ -36091,7 +36091,7 @@
       </c>
       <c r="G373" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H373" s="11" t="inlineStr">
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G374" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H374" s="11" t="inlineStr">
@@ -36231,7 +36231,7 @@
       </c>
       <c r="G375" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H375" s="11" t="inlineStr">
@@ -36301,7 +36301,7 @@
       </c>
       <c r="G376" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H376" s="11" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="G377" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H377" s="11" t="inlineStr">
@@ -36441,7 +36441,7 @@
       </c>
       <c r="G378" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H378" s="11" t="inlineStr">
@@ -36511,7 +36511,7 @@
       </c>
       <c r="G379" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H379" s="11" t="inlineStr">
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G380" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H380" s="11" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H381" s="11" t="inlineStr">
@@ -36721,7 +36721,7 @@
       </c>
       <c r="G382" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H382" s="11" t="inlineStr">
@@ -36791,7 +36791,7 @@
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H383" s="11" t="inlineStr">
@@ -36861,7 +36861,7 @@
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H384" s="11" t="inlineStr">
@@ -36931,7 +36931,7 @@
       </c>
       <c r="G385" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H385" s="11" t="inlineStr">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="G386" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H386" s="11" t="inlineStr">
@@ -37071,7 +37071,7 @@
       </c>
       <c r="G387" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H387" s="11" t="inlineStr">
@@ -37141,7 +37141,7 @@
       </c>
       <c r="G388" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H388" s="11" t="inlineStr">
@@ -37211,7 +37211,7 @@
       </c>
       <c r="G389" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H389" s="11" t="inlineStr">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="G390" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H390" s="11" t="inlineStr">
@@ -37351,7 +37351,7 @@
       </c>
       <c r="G391" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H391" s="11" t="inlineStr">
@@ -37421,7 +37421,7 @@
       </c>
       <c r="G392" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H392" s="11" t="inlineStr">
@@ -37491,7 +37491,7 @@
       </c>
       <c r="G393" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H393" s="11" t="inlineStr">
@@ -37561,7 +37561,7 @@
       </c>
       <c r="G394" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H394" s="11" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="G395" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H395" s="11" t="inlineStr">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="G396" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H396" s="11" t="inlineStr">
@@ -42819,7 +42819,7 @@
       </c>
       <c r="G469" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H469" s="11" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="G470" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H470" s="11" t="inlineStr">
@@ -42963,7 +42963,7 @@
       </c>
       <c r="G471" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H471" s="11" t="inlineStr">
@@ -43033,7 +43033,7 @@
       </c>
       <c r="G472" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H472" s="11" t="inlineStr">
@@ -43103,7 +43103,7 @@
       </c>
       <c r="G473" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H473" s="11" t="inlineStr">
@@ -43173,7 +43173,7 @@
       </c>
       <c r="G474" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H474" s="11" t="inlineStr">
@@ -43243,7 +43243,7 @@
       </c>
       <c r="G475" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H475" s="11" t="inlineStr">
@@ -43313,7 +43313,7 @@
       </c>
       <c r="G476" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H476" s="11" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="G477" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H477" s="11" t="inlineStr">
@@ -45355,7 +45355,7 @@
       </c>
       <c r="G505" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H505" s="14" t="inlineStr">
@@ -45429,7 +45429,7 @@
       </c>
       <c r="G506" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H506" s="14" t="inlineStr">
@@ -45499,7 +45499,7 @@
       </c>
       <c r="G507" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H507" s="14" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="G508" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H508" s="14" t="inlineStr">
@@ -45639,7 +45639,7 @@
       </c>
       <c r="G509" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H509" s="14" t="inlineStr">
@@ -45709,7 +45709,7 @@
       </c>
       <c r="G510" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H510" s="14" t="inlineStr">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="G511" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H511" s="14" t="inlineStr">
@@ -45849,7 +45849,7 @@
       </c>
       <c r="G512" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H512" s="14" t="inlineStr">
@@ -45919,7 +45919,7 @@
       </c>
       <c r="G513" s="14" t="inlineStr">
         <is>
-          <t>Timing at 1.30× pickup</t>
+          <t>Timing at 1.3× pickup</t>
         </is>
       </c>
       <c r="H513" s="14" t="inlineStr">
@@ -46977,7 +46977,7 @@
       </c>
       <c r="G528" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="H528" s="14" t="inlineStr">
@@ -47047,7 +47047,7 @@
       </c>
       <c r="G529" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="H529" s="14" t="inlineStr">
@@ -47117,7 +47117,7 @@
       </c>
       <c r="G530" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="H530" s="14" t="inlineStr">
@@ -47187,7 +47187,7 @@
       </c>
       <c r="G531" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="H531" s="14" t="inlineStr">
@@ -47257,7 +47257,7 @@
       </c>
       <c r="G532" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="H532" s="14" t="inlineStr">
@@ -47327,7 +47327,7 @@
       </c>
       <c r="G533" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — above threshold</t>
+          <t>60 Hz — above threshold</t>
         </is>
       </c>
       <c r="H533" s="14" t="inlineStr">
@@ -47397,7 +47397,7 @@
       </c>
       <c r="G534" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="H534" s="14" t="inlineStr">
@@ -47467,7 +47467,7 @@
       </c>
       <c r="G535" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="H535" s="14" t="inlineStr">
@@ -47537,7 +47537,7 @@
       </c>
       <c r="G536" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="H536" s="14" t="inlineStr">
@@ -47607,7 +47607,7 @@
       </c>
       <c r="G537" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="H537" s="14" t="inlineStr">
@@ -47677,7 +47677,7 @@
       </c>
       <c r="G538" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="H538" s="14" t="inlineStr">
@@ -47747,7 +47747,7 @@
       </c>
       <c r="G539" s="14" t="inlineStr">
         <is>
-          <t>60.0 Hz — below threshold</t>
+          <t>60 Hz — below threshold</t>
         </is>
       </c>
       <c r="H539" s="14" t="inlineStr">
@@ -47817,7 +47817,7 @@
       </c>
       <c r="G540" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="H540" s="14" t="inlineStr">
@@ -47887,7 +47887,7 @@
       </c>
       <c r="G541" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="H541" s="14" t="inlineStr">
@@ -47957,7 +47957,7 @@
       </c>
       <c r="G542" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="H542" s="14" t="inlineStr">
@@ -48027,7 +48027,7 @@
       </c>
       <c r="G543" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="H543" s="14" t="inlineStr">
@@ -48097,7 +48097,7 @@
       </c>
       <c r="G544" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="H544" s="14" t="inlineStr">
@@ -48167,7 +48167,7 @@
       </c>
       <c r="G545" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — above threshold</t>
+          <t>57 Hz — above threshold</t>
         </is>
       </c>
       <c r="H545" s="14" t="inlineStr">
@@ -48237,7 +48237,7 @@
       </c>
       <c r="G546" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="H546" s="14" t="inlineStr">
@@ -48307,7 +48307,7 @@
       </c>
       <c r="G547" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="H547" s="14" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="G548" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="H548" s="14" t="inlineStr">
@@ -48447,7 +48447,7 @@
       </c>
       <c r="G549" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="H549" s="14" t="inlineStr">
@@ -48517,7 +48517,7 @@
       </c>
       <c r="G550" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="H550" s="14" t="inlineStr">
@@ -48587,7 +48587,7 @@
       </c>
       <c r="G551" s="14" t="inlineStr">
         <is>
-          <t>57.0 Hz — below threshold</t>
+          <t>57 Hz — below threshold</t>
         </is>
       </c>
       <c r="H551" s="14" t="inlineStr">
@@ -48657,7 +48657,7 @@
       </c>
       <c r="G552" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="H552" s="14" t="inlineStr">
@@ -48727,7 +48727,7 @@
       </c>
       <c r="G553" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="H553" s="14" t="inlineStr">
@@ -48797,7 +48797,7 @@
       </c>
       <c r="G554" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="H554" s="14" t="inlineStr">
@@ -48867,7 +48867,7 @@
       </c>
       <c r="G555" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="H555" s="14" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="G556" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="H556" s="14" t="inlineStr">
@@ -49007,7 +49007,7 @@
       </c>
       <c r="G557" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — above threshold</t>
+          <t>54 Hz — above threshold</t>
         </is>
       </c>
       <c r="H557" s="14" t="inlineStr">
@@ -49077,7 +49077,7 @@
       </c>
       <c r="G558" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="H558" s="14" t="inlineStr">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="G559" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="H559" s="14" t="inlineStr">
@@ -49217,7 +49217,7 @@
       </c>
       <c r="G560" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="H560" s="14" t="inlineStr">
@@ -49287,7 +49287,7 @@
       </c>
       <c r="G561" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="H561" s="14" t="inlineStr">
@@ -49357,7 +49357,7 @@
       </c>
       <c r="G562" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="H562" s="14" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="G563" s="14" t="inlineStr">
         <is>
-          <t>54.0 Hz — below threshold</t>
+          <t>54 Hz — below threshold</t>
         </is>
       </c>
       <c r="H563" s="14" t="inlineStr">
@@ -53091,7 +53091,7 @@
       </c>
       <c r="G615" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H615" s="11" t="inlineStr">
@@ -53161,7 +53161,7 @@
       </c>
       <c r="G616" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H616" s="11" t="inlineStr">
@@ -53231,7 +53231,7 @@
       </c>
       <c r="G617" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H617" s="11" t="inlineStr">
@@ -53301,7 +53301,7 @@
       </c>
       <c r="G618" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H618" s="11" t="inlineStr">
@@ -53371,7 +53371,7 @@
       </c>
       <c r="G619" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H619" s="11" t="inlineStr">
@@ -53441,7 +53441,7 @@
       </c>
       <c r="G620" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H620" s="11" t="inlineStr">
@@ -53511,7 +53511,7 @@
       </c>
       <c r="G621" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H621" s="11" t="inlineStr">
@@ -53581,7 +53581,7 @@
       </c>
       <c r="G622" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H622" s="11" t="inlineStr">
@@ -53651,7 +53651,7 @@
       </c>
       <c r="G623" s="11" t="inlineStr">
         <is>
-          <t>Operate at 1.50× thermal setting</t>
+          <t>Operate at 1.5× thermal setting</t>
         </is>
       </c>
       <c r="H623" s="11" t="inlineStr">
@@ -53721,7 +53721,7 @@
       </c>
       <c r="G624" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H624" s="11" t="inlineStr">
@@ -53791,7 +53791,7 @@
       </c>
       <c r="G625" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H625" s="11" t="inlineStr">
@@ -53861,7 +53861,7 @@
       </c>
       <c r="G626" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H626" s="11" t="inlineStr">
@@ -53931,7 +53931,7 @@
       </c>
       <c r="G627" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H627" s="11" t="inlineStr">
@@ -54001,7 +54001,7 @@
       </c>
       <c r="G628" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H628" s="11" t="inlineStr">
@@ -54071,7 +54071,7 @@
       </c>
       <c r="G629" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H629" s="11" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="G630" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H630" s="11" t="inlineStr">
@@ -54211,7 +54211,7 @@
       </c>
       <c r="G631" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H631" s="11" t="inlineStr">
@@ -54281,7 +54281,7 @@
       </c>
       <c r="G632" s="11" t="inlineStr">
         <is>
-          <t>Operate at 2.00× thermal setting</t>
+          <t>Operate at 2× thermal setting</t>
         </is>
       </c>
       <c r="H632" s="11" t="inlineStr">
@@ -54351,7 +54351,7 @@
       </c>
       <c r="G633" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H633" s="11" t="inlineStr">
@@ -54421,7 +54421,7 @@
       </c>
       <c r="G634" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H634" s="11" t="inlineStr">
@@ -54491,7 +54491,7 @@
       </c>
       <c r="G635" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H635" s="11" t="inlineStr">
@@ -54561,7 +54561,7 @@
       </c>
       <c r="G636" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H636" s="11" t="inlineStr">
@@ -54631,7 +54631,7 @@
       </c>
       <c r="G637" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H637" s="11" t="inlineStr">
@@ -54701,7 +54701,7 @@
       </c>
       <c r="G638" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H638" s="11" t="inlineStr">
@@ -54771,7 +54771,7 @@
       </c>
       <c r="G639" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H639" s="11" t="inlineStr">
@@ -54841,7 +54841,7 @@
       </c>
       <c r="G640" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H640" s="11" t="inlineStr">
@@ -54911,7 +54911,7 @@
       </c>
       <c r="G641" s="11" t="inlineStr">
         <is>
-          <t>Operate at 3.00× thermal setting</t>
+          <t>Operate at 3× thermal setting</t>
         </is>
       </c>
       <c r="H641" s="11" t="inlineStr">
@@ -54981,7 +54981,7 @@
       </c>
       <c r="G642" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H642" s="11" t="inlineStr">
@@ -55051,7 +55051,7 @@
       </c>
       <c r="G643" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H643" s="11" t="inlineStr">
@@ -55121,7 +55121,7 @@
       </c>
       <c r="G644" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H644" s="11" t="inlineStr">
@@ -55191,7 +55191,7 @@
       </c>
       <c r="G645" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H645" s="11" t="inlineStr">
@@ -55261,7 +55261,7 @@
       </c>
       <c r="G646" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H646" s="11" t="inlineStr">
@@ -55331,7 +55331,7 @@
       </c>
       <c r="G647" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H647" s="11" t="inlineStr">
@@ -55401,7 +55401,7 @@
       </c>
       <c r="G648" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H648" s="11" t="inlineStr">
@@ -55471,7 +55471,7 @@
       </c>
       <c r="G649" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H649" s="11" t="inlineStr">
@@ -55541,7 +55541,7 @@
       </c>
       <c r="G650" s="11" t="inlineStr">
         <is>
-          <t>Operate at 5.00× thermal setting</t>
+          <t>Operate at 5× thermal setting</t>
         </is>
       </c>
       <c r="H650" s="11" t="inlineStr">
@@ -62258,7 +62258,7 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>W2. Enter your real transformer in `index.html` and re-run the generator.</t>
+          <t>W2. Enter your real transformer in `845.html` and re-run the generator.</t>
         </is>
       </c>
     </row>

--- a/omicron/xlsx/845-VEC-test-plan.xlsx
+++ b/omicron/xlsx/845-VEC-test-plan.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>generated 2026-09-15 00:38 from src/845-vec.html</t>
+          <t>generated 2026-09-15 01:39 from src/845-vec.html</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Idiff required 0.200 pu · applied 0.220 pu (+10%)</t>
+          <t>Idiff required 0.375 pu · applied 0.413 pu (+10%)</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="O4" s="12" t="inlineStr">
         <is>
-          <t>4.4626@150.0</t>
+          <t>3.7915@150.0</t>
         </is>
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>4.4626@30.0</t>
+          <t>3.7915@30.0</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr">
         <is>
-          <t>4.4626@-90.0</t>
+          <t>3.7915@-90.0</t>
         </is>
       </c>
       <c r="R4" s="12" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="U4" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="V4" s="13" t="n"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Idiff required 0.200 pu · applied 0.180 pu (−10%)</t>
+          <t>Idiff required 0.375 pu · applied 0.338 pu (−10%)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
-          <t>4.6021@150.0</t>
+          <t>4.0530@150.0</t>
         </is>
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>4.6021@30.0</t>
+          <t>4.0530@30.0</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
-          <t>4.6021@-90.0</t>
+          <t>4.0530@-90.0</t>
         </is>
       </c>
       <c r="R5" s="12" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="U5" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="V5" s="13" t="n"/>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P20" s="12" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P24" s="12" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -11762,7 +11762,7 @@
         </is>
       </c>
       <c r="I26" s="12" t="n">
-        <v>4.4626</v>
+        <v>3.7915</v>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P26" s="12" t="inlineStr">
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="I27" s="12" t="n">
-        <v>4.4626</v>
+        <v>3.7915</v>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="I28" s="12" t="n">
-        <v>4.4626</v>
+        <v>3.7915</v>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.280 pu</t>
+          <t>IW1 1.500 pu · IW2 1.087 pu</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P30" s="12" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="I35" s="12" t="n">
-        <v>4.6021</v>
+        <v>4.053</v>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -12462,7 +12462,7 @@
         </is>
       </c>
       <c r="I36" s="12" t="n">
-        <v>4.6021</v>
+        <v>4.053</v>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="I37" s="12" t="n">
-        <v>4.6021</v>
+        <v>4.053</v>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>IW1 1.500 pu · IW2 1.320 pu</t>
+          <t>IW1 1.500 pu · IW2 1.163 pu</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
